--- a/Result/profitability/6279.xlsx
+++ b/Result/profitability/6279.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.54</v>
       </c>
       <c r="M2" t="n">
-        <v>2.48625</v>
+        <v>2.455</v>
       </c>
       <c r="N2" t="n">
-        <v>31.3025</v>
+        <v>30.79625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>1.5</v>
       </c>
       <c r="M3" t="n">
-        <v>2.2925</v>
+        <v>2.18</v>
       </c>
       <c r="N3" t="n">
-        <v>32.305</v>
+        <v>31.545</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.97</v>
       </c>
       <c r="M4" t="n">
-        <v>1.95125</v>
+        <v>1.9075</v>
       </c>
       <c r="N4" t="n">
-        <v>32.455</v>
+        <v>31.98375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.45</v>
       </c>
       <c r="M5" t="n">
-        <v>1.50125</v>
+        <v>1.75125</v>
       </c>
       <c r="N5" t="n">
-        <v>30.3475</v>
+        <v>29.65125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.59</v>
       </c>
       <c r="M6" t="n">
-        <v>1.475</v>
+        <v>1.5075</v>
       </c>
       <c r="N6" t="n">
-        <v>30.16375</v>
+        <v>29.95125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,13 +1264,13 @@
         <v>1.07</v>
       </c>
       <c r="M7" t="n">
-        <v>1.29125</v>
+        <v>1.0775</v>
       </c>
       <c r="N7" t="n">
-        <v>31.94625</v>
+        <v>31.54</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1282,7 +1282,7 @@
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>1.23</v>
       </c>
       <c r="M8" t="n">
-        <v>0.88125</v>
+        <v>1.03125</v>
       </c>
       <c r="N8" t="n">
-        <v>33.14875</v>
+        <v>33.30875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6279</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2747</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1979</v>
+      </c>
+      <c r="E75" t="n">
+        <v>767</v>
+      </c>
+      <c r="F75" t="n">
+        <v>27.93</v>
+      </c>
+      <c r="G75" t="n">
+        <v>381</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>13.87%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>33</v>
+      </c>
+      <c r="J75" t="n">
+        <v>414</v>
+      </c>
+      <c r="K75" t="n">
+        <v>333</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2.76875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>30.8225</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.7499999999999998</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.280000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.04803001876172619</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-5.57</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1662686567164179</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
